--- a/diseases/d198/2015-2019.xlsx
+++ b/diseases/d198/2015-2019.xlsx
@@ -776,6 +776,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1057,6 +1067,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1193,6 +1208,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1329,6 +1349,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1465,6 +1490,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1601,6 +1631,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1737,6 +1772,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1873,6 +1913,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2009,6 +2054,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2145,6 +2195,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2281,6 +2336,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2417,6 +2477,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2553,6 +2618,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2689,6 +2759,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2825,6 +2900,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2961,6 +3041,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3097,6 +3182,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3233,6 +3323,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3369,6 +3464,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3505,6 +3605,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3641,6 +3746,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3777,6 +3887,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3913,6 +4028,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4049,6 +4169,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4185,6 +4310,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4321,6 +4451,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4457,6 +4592,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4596,6 +4736,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4741,6 +4886,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4877,6 +5027,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5013,6 +5168,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5149,6 +5309,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5285,6 +5450,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5421,6 +5591,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5557,6 +5732,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5693,6 +5873,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5829,6 +6014,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5965,6 +6155,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6101,6 +6296,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6237,6 +6437,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6373,6 +6578,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6509,6 +6719,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6645,6 +6860,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6781,6 +7001,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6917,6 +7142,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7053,6 +7283,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7189,6 +7424,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7325,6 +7565,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7461,6 +7706,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7597,6 +7847,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7733,6 +7988,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7869,6 +8129,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8005,6 +8270,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8141,6 +8411,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8277,6 +8552,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8416,6 +8696,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8561,6 +8846,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8697,6 +8987,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8833,6 +9128,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8969,6 +9269,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9105,6 +9410,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9241,6 +9551,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9377,6 +9692,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9513,6 +9833,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9649,6 +9974,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9785,6 +10115,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9921,6 +10256,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10057,6 +10397,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10193,6 +10538,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10329,6 +10679,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10465,6 +10820,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10601,6 +10961,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10737,6 +11102,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10873,6 +11243,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11009,6 +11384,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11145,6 +11525,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11281,6 +11666,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11417,6 +11807,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11553,6 +11948,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11689,6 +12089,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11825,6 +12230,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11961,6 +12371,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12097,6 +12512,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12236,6 +12656,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12381,6 +12806,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12517,6 +12947,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12653,6 +13088,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12789,6 +13229,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12925,6 +13370,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13061,6 +13511,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13197,6 +13652,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13333,6 +13793,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13469,6 +13934,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13605,6 +14075,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13741,6 +14216,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13877,6 +14357,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14013,6 +14498,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14149,6 +14639,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14285,6 +14780,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14421,6 +14921,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14557,6 +15062,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14693,6 +15203,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14829,6 +15344,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14965,6 +15485,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15101,6 +15626,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15237,6 +15767,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15373,6 +15908,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15509,6 +16049,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15645,6 +16190,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15781,6 +16331,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15917,6 +16472,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16056,6 +16616,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16201,6 +16766,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16337,6 +16907,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16473,6 +17048,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16609,6 +17189,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16745,6 +17330,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16881,6 +17471,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17017,6 +17612,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17153,6 +17753,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17289,6 +17894,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17425,6 +18035,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17561,6 +18176,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17697,6 +18317,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17833,6 +18458,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17969,6 +18599,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18105,6 +18740,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18241,6 +18881,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18377,6 +19022,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18513,6 +19163,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18649,6 +19304,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18785,6 +19445,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18921,6 +19586,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19057,6 +19727,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19193,6 +19868,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19329,6 +20009,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19465,6 +20150,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19601,6 +20291,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19737,6 +20432,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19876,6 +20576,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20021,6 +20726,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20157,6 +20867,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20293,6 +21008,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20429,6 +21149,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20565,6 +21290,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20701,6 +21431,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20837,6 +21572,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20973,6 +21713,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21109,6 +21854,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21245,6 +21995,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21381,6 +22136,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21517,6 +22277,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21653,6 +22418,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21789,6 +22559,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21925,6 +22700,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22061,6 +22841,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22197,6 +22982,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22333,6 +23123,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22469,6 +23264,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22605,6 +23405,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22741,6 +23546,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22877,6 +23687,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23013,6 +23828,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23149,6 +23969,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23285,6 +24110,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23421,6 +24251,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23557,6 +24392,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23696,6 +24536,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23841,6 +24686,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23977,6 +24827,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24113,6 +24968,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24249,6 +25109,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24385,6 +25250,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24521,6 +25391,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24657,6 +25532,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24793,6 +25673,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24929,6 +25814,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25065,6 +25955,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25201,6 +26096,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25337,6 +26237,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25473,6 +26378,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25609,6 +26519,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25745,6 +26660,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25881,6 +26801,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26017,6 +26942,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26153,6 +27083,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26289,6 +27224,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26425,6 +27365,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26561,6 +27506,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26697,6 +27647,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26833,6 +27788,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26969,6 +27929,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27105,6 +28070,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27241,6 +28211,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27377,6 +28352,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27516,6 +28496,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27661,6 +28646,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27797,6 +28787,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27933,6 +28928,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28069,6 +29069,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28205,6 +29210,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28341,6 +29351,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28477,6 +29492,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28613,6 +29633,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28749,6 +29774,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28885,6 +29915,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29021,6 +30056,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29157,6 +30197,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29293,6 +30338,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29429,6 +30479,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29565,6 +30620,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29701,6 +30761,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29837,6 +30902,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29973,6 +31043,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30109,6 +31184,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30245,6 +31325,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30381,6 +31466,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30517,6 +31607,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30653,6 +31748,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30789,6 +31889,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30925,6 +32030,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31061,6 +32171,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31197,6 +32312,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31336,6 +32456,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31481,6 +32606,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31617,6 +32747,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31753,6 +32888,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31889,6 +33029,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32025,6 +33170,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32161,6 +33311,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32297,6 +33452,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32433,6 +33593,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32569,6 +33734,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32705,6 +33875,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32841,6 +34016,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32977,6 +34157,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33113,6 +34298,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33249,6 +34439,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33385,6 +34580,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33521,6 +34721,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33657,6 +34862,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33793,6 +35003,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33929,6 +35144,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34065,6 +35285,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34201,6 +35426,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34337,6 +35567,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34473,6 +35708,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34609,6 +35849,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34745,6 +35990,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34881,6 +36131,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35017,6 +36272,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35156,6 +36416,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35301,6 +36566,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35437,6 +36707,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35573,6 +36848,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35709,6 +36989,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35845,6 +37130,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35981,6 +37271,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36117,6 +37412,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36253,6 +37553,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36389,6 +37694,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36525,6 +37835,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36661,6 +37976,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36797,6 +38117,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36933,6 +38258,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37069,6 +38399,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37205,6 +38540,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37341,6 +38681,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37477,6 +38822,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37613,6 +38963,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37749,6 +39104,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37885,6 +39245,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38021,6 +39386,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38157,6 +39527,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38293,6 +39668,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38429,6 +39809,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38565,6 +39950,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38701,6 +40091,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38837,6 +40232,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38976,6 +40376,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39121,6 +40526,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39257,6 +40667,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39393,6 +40808,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39529,6 +40949,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39665,6 +41090,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39801,6 +41231,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39937,6 +41372,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO289" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40073,6 +41513,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40209,6 +41654,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO291" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40345,6 +41795,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO292" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40481,6 +41936,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO293" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40617,6 +42077,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO294" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40753,6 +42218,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40889,6 +42359,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO296" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41025,6 +42500,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO297" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41161,6 +42641,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO298" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41297,6 +42782,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO299" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41433,6 +42923,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41569,6 +43064,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41705,6 +43205,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO302" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41841,6 +43346,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO303" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41977,6 +43487,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO304" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42113,6 +43628,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO305" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42249,6 +43769,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42385,6 +43910,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42521,6 +44051,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO308" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42657,6 +44192,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO309" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42796,6 +44336,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO310" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42941,6 +44486,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO311" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43077,6 +44627,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43213,6 +44768,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO313" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43349,6 +44909,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43485,6 +45050,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO315" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43621,6 +45191,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO316" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43757,6 +45332,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO317" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43893,6 +45473,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44029,6 +45614,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO319" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44165,6 +45755,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO320" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44301,6 +45896,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO321" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44437,6 +46037,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO322" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44573,6 +46178,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44709,6 +46319,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO324" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44845,6 +46460,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO325" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44981,6 +46601,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO326" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45117,6 +46742,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO327" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45253,6 +46883,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO328" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45389,6 +47024,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO329" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45525,6 +47165,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO330" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45661,6 +47306,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO331" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45797,6 +47447,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO332" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45933,6 +47588,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO333" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46069,6 +47729,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO334" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46205,6 +47870,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO335" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46341,6 +48011,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO336" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46475,6 +48150,11 @@
       <c r="S337" t="inlineStr">
         <is>
           <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO337" t="inlineStr">
